--- a/КПП/Том СКС КПП/Журнал входного контроля СКС КПП.xlsx
+++ b/КПП/Том СКС КПП/Журнал входного контроля СКС КПП.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Розетка коммутационная RJ-45 в кабель-канале, BRAVA RJ45 / Cabeus RJ-45 кат. 6 экр. (спецификация .СО, поз. 3, 4) (поз. XS)</t>
+          <t>Розетка компьютерная RJ-45 кат. 6, накладная, Cabeus RJ-45 (8P8C) кат. 6 (поз. XS)</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>DKC / Cabeus</t>
+          <t>Cabeus</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Розетка коммутационная (для аналогового телефона), BRAVA RJ45 (спецификация .СО, поз. 3) (поз. X)</t>
+          <t>Розетка компьютерная RJ-45 кат. 6 в кабель-канале, BRAVA RJ45 (поз. XS)</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="F30" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Радиотелефон, Panasonic KX-TG6811RUB</t>
+          <t>Розетка телефонная RJ-45 кат. 5e в кабель-канале, BRAVA RJ45 (поз. X)</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>DKC</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F31" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Системный телефон, STA30G</t>
+          <t>Радиотелефон, Panasonic KX-TG6811RUB</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>MAXICOM</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Телефон проводной, TeXet TX-241</t>
+          <t>Системный телефон, STA30G</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>teXet</t>
+          <t>MAXICOM</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -1632,91 +1632,144 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
+          <t>Телефон проводной, TeXet TX-241</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>teXet</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>Соответствует. Допущено к применению</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Иванчук М.В.</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
+        <is>
+          <t>ИД лист 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
           <t>IP-телефон, Fanvil X301P</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Fanvil</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F35" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>Паспорт (руководство по эксплуатации) изготовителя</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>Соответствует. Допущено к применению</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>Иванчук М.В.</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>ИД лист 2</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности ООО «АльтЭн» Иванчук М.В.</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="I38" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Представитель лица, осуществляющего строительство</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
@@ -1724,25 +1777,25 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="I41:K41"/>
     <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="I37:K37"/>
     <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A6:K6"/>
+    <mergeCell ref="G38:H38"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="I38:K38"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="I40:K40"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A8:K8"/>
+    <mergeCell ref="G41:H41"/>
     <mergeCell ref="A10:K10"/>
-    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
